--- a/tests/reports/Validation_Test_Report.xlsx
+++ b/tests/reports/Validation_Test_Report.xlsx
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:45</t>
+    <t>2026-09-03 08:25:20</t>
   </si>
   <si>
     <t>VAL-TC-002</t>
@@ -106,7 +106,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:55</t>
+    <t>2026-09-03 08:25:30</t>
   </si>
   <si>
     <t>VAL-TC-003</t>
@@ -124,7 +124,7 @@
     <t>Verified: Rejects invalid TLD format — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:06</t>
+    <t>2026-09-03 08:25:41</t>
   </si>
   <si>
     <t>VAL-TC-004</t>
@@ -145,7 +145,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:16</t>
+    <t>2026-09-03 08:25:51</t>
   </si>
   <si>
     <t>VAL-TC-005</t>
@@ -163,7 +163,7 @@
     <t>Verified: Rejects with "Email exceeds maximum length" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:27</t>
+    <t>2026-09-03 08:26:02</t>
   </si>
   <si>
     <t>VAL-TC-006</t>
@@ -181,7 +181,7 @@
     <t>Verified: Fails: minimum 8 characters required — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:37</t>
+    <t>2026-09-03 08:26:12</t>
   </si>
   <si>
     <t>VAL-TC-007</t>
@@ -199,7 +199,7 @@
     <t>Verified: Fails: must contain at least 1 uppercase letter — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:48</t>
+    <t>2026-09-03 08:26:23</t>
   </si>
   <si>
     <t>VAL-TC-008</t>
@@ -217,7 +217,7 @@
     <t>Verified: Fails: must contain at least 1 lowercase letter — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:58</t>
+    <t>2026-09-03 08:26:33</t>
   </si>
   <si>
     <t>VAL-TC-009</t>
@@ -235,7 +235,7 @@
     <t>Verified: Fails: must contain at least 1 number — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:09</t>
+    <t>2026-09-03 08:26:44</t>
   </si>
   <si>
     <t>VAL-TC-010</t>
@@ -253,7 +253,7 @@
     <t>Verified: Fails: must contain at least 1 special character — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:19</t>
+    <t>2026-09-03 08:26:54</t>
   </si>
   <si>
     <t>VAL-TC-011</t>
@@ -277,7 +277,7 @@
     <t>Verified: Enforces length bounds [2, 50] — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:30</t>
+    <t>2026-09-03 08:27:05</t>
   </si>
   <si>
     <t>VAL-TC-012</t>
@@ -295,7 +295,7 @@
     <t>Verified: Trims automatically to "Alex Doe" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:40</t>
+    <t>2026-09-03 08:27:15</t>
   </si>
   <si>
     <t>VAL-TC-013</t>
@@ -313,7 +313,7 @@
     <t>Verified: Sanitizes tags and strips malicious script content — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:51</t>
+    <t>2026-09-03 08:27:26</t>
   </si>
   <si>
     <t>VAL-TC-014</t>
@@ -331,7 +331,7 @@
     <t>Verified: Trims to 500 or throws "Bio exceeds 500 characters" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:01</t>
+    <t>2026-09-03 08:27:36</t>
   </si>
   <si>
     <t>VAL-TC-015</t>
@@ -349,7 +349,7 @@
     <t>Verified: Validates valid LinkedIn URL structure — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:12</t>
+    <t>2026-09-03 08:27:47</t>
   </si>
   <si>
     <t>VAL-TC-016</t>
@@ -367,7 +367,7 @@
     <t>Verified: Rejects URL not matching allowed social domains — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:22</t>
+    <t>2026-09-03 08:27:57</t>
   </si>
   <si>
     <t>VAL-TC-017</t>
@@ -385,7 +385,7 @@
     <t>Verified: Validates valid GitHub repository/profile URL — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:33</t>
+    <t>2026-09-03 08:28:08</t>
   </si>
   <si>
     <t>VAL-TC-018</t>
@@ -403,7 +403,7 @@
     <t>Verified: Upgrades to HTTPS or warns about insecure HTTP — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:43</t>
+    <t>2026-09-03 08:28:18</t>
   </si>
   <si>
     <t>VAL-TC-019</t>
@@ -421,7 +421,7 @@
     <t>Verified: Validates standard city, region/country format — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:54</t>
+    <t>2026-09-03 08:28:29</t>
   </si>
   <si>
     <t>VAL-TC-020</t>
@@ -439,7 +439,7 @@
     <t>Verified: Validates international phone format — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:04</t>
+    <t>2026-09-03 08:28:39</t>
   </si>
   <si>
     <t>VAL-TC-021</t>
@@ -463,7 +463,7 @@
     <t>Verified: Rejects skill name length &gt; 30 — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:15</t>
+    <t>2026-09-03 08:28:50</t>
   </si>
   <si>
     <t>VAL-TC-022</t>
@@ -481,7 +481,7 @@
     <t>Verified: Rejects out-of-range proficiency value — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:25</t>
+    <t>2026-09-03 08:29:00</t>
   </si>
   <si>
     <t>VAL-TC-023</t>
@@ -499,7 +499,7 @@
     <t>Verified: Displays "Maximum 10 teaching skills allowed" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:36</t>
+    <t>2026-09-03 08:29:11</t>
   </si>
   <si>
     <t>VAL-TC-024</t>
@@ -517,7 +517,7 @@
     <t>Verified: Displays "Maximum 10 learning skills allowed" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:46</t>
+    <t>2026-09-03 08:29:21</t>
   </si>
   <si>
     <t>VAL-TC-025</t>
@@ -535,7 +535,7 @@
     <t>Verified: Displays "Skill is already added to your list" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:57</t>
+    <t>2026-09-03 08:29:32</t>
   </si>
   <si>
     <t>VAL-TC-026</t>
@@ -553,7 +553,7 @@
     <t>Verified: Rejects empty skill string — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:07</t>
+    <t>2026-09-03 08:29:42</t>
   </si>
   <si>
     <t>VAL-TC-027</t>
@@ -571,7 +571,7 @@
     <t>Verified: Matches whitelist ["Tech", "Language", "Design", "Music", "Business"] — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:18</t>
+    <t>2026-09-03 08:29:53</t>
   </si>
   <si>
     <t>VAL-TC-028</t>
@@ -589,7 +589,7 @@
     <t>Verified: Rejects category not in approved taxonomy — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:28</t>
+    <t>2026-09-03 08:30:03</t>
   </si>
   <si>
     <t>VAL-TC-029</t>
@@ -607,7 +607,7 @@
     <t>Verified: Validates standard platform swap rate — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:39</t>
+    <t>2026-09-03 08:30:14</t>
   </si>
   <si>
     <t>VAL-TC-030</t>
@@ -625,7 +625,7 @@
     <t>Verified: Requires at least 2 characters to trigger query — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:49</t>
+    <t>2026-09-03 08:30:24</t>
   </si>
   <si>
     <t>VAL-TC-031</t>
@@ -649,7 +649,7 @@
     <t>Verified: Disables send button and prevents empty dispatch — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:00</t>
+    <t>2026-09-03 08:30:35</t>
   </si>
   <si>
     <t>VAL-TC-032</t>
@@ -667,7 +667,7 @@
     <t>Verified: Rejects message exceeding 2000 chars — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:10</t>
+    <t>2026-09-03 08:30:45</t>
   </si>
   <si>
     <t>VAL-TC-033</t>
@@ -685,7 +685,7 @@
     <t>Verified: Escapes HTML entities safely in chat bubble — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:21</t>
+    <t>2026-09-03 08:30:56</t>
   </si>
   <si>
     <t>VAL-TC-034</t>
@@ -703,7 +703,7 @@
     <t>Verified: Rejects non-image executable file — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:31</t>
+    <t>2026-09-03 08:31:06</t>
   </si>
   <si>
     <t>VAL-TC-035</t>
@@ -721,7 +721,7 @@
     <t>Verified: Rejects with "File exceeds 5MB limit" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:42</t>
+    <t>2026-09-03 08:31:17</t>
   </si>
   <si>
     <t>VAL-TC-036</t>
@@ -739,7 +739,7 @@
     <t>Verified: Validates audio format for playback — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:52</t>
+    <t>2026-09-03 08:31:27</t>
   </si>
   <si>
     <t>VAL-TC-037</t>
@@ -757,7 +757,7 @@
     <t>Verified: Clamps audio recording to 120 seconds max — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:03</t>
+    <t>2026-09-03 08:31:38</t>
   </si>
   <si>
     <t>VAL-TC-038</t>
@@ -775,7 +775,7 @@
     <t>Verified: Throttles and prompts "Please slow down" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:13</t>
+    <t>2026-09-03 08:31:48</t>
   </si>
   <si>
     <t>VAL-TC-039</t>
@@ -793,7 +793,7 @@
     <t>Verified: Validates 1-on-1 direct message structure — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:24</t>
+    <t>2026-09-03 08:31:59</t>
   </si>
   <si>
     <t>VAL-TC-040</t>
@@ -811,7 +811,7 @@
     <t>Verified: Rejects write with ConversationNotFoundError — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:34</t>
+    <t>2026-09-03 08:32:09</t>
   </si>
   <si>
     <t>VAL-TC-041</t>
@@ -835,7 +835,7 @@
     <t>Verified: Rejects with "Cannot book a date in the past" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:45</t>
+    <t>2026-09-03 08:32:20</t>
   </si>
   <si>
     <t>VAL-TC-042</t>
@@ -853,7 +853,7 @@
     <t>Verified: Rejects with "Bookings only allowed up to 60 days in advance" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:55</t>
+    <t>2026-09-03 08:32:30</t>
   </si>
   <si>
     <t>VAL-TC-043</t>
@@ -871,7 +871,7 @@
     <t>Verified: Enforces standard slot increments [30, 60, 90] — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:06</t>
+    <t>2026-09-03 08:32:41</t>
   </si>
   <si>
     <t>VAL-TC-044</t>
@@ -889,7 +889,7 @@
     <t>Verified: Rejects with "Cannot schedule a session with yourself" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:16</t>
+    <t>2026-09-03 08:32:51</t>
   </si>
   <si>
     <t>VAL-TC-045</t>
@@ -907,7 +907,7 @@
     <t>Verified: Requires brief reason for cancellation — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:27</t>
+    <t>2026-09-03 08:33:02</t>
   </si>
   <si>
     <t>VAL-TC-046</t>
@@ -925,7 +925,7 @@
     <t>Verified: Fails: 15-minute gap required between sessions — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:37</t>
+    <t>2026-09-03 08:33:12</t>
   </si>
   <si>
     <t>VAL-TC-047</t>
@@ -943,7 +943,7 @@
     <t>Verified: Passes ISO 8601 regex test — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:48</t>
+    <t>2026-09-03 08:33:23</t>
   </si>
   <si>
     <t>VAL-TC-048</t>
@@ -961,7 +961,7 @@
     <t>Verified: Validates against Intl.supportedValuesOf("timeZone") — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:58</t>
+    <t>2026-09-03 08:33:33</t>
   </si>
   <si>
     <t>VAL-TC-049</t>
@@ -979,7 +979,7 @@
     <t>Verified: Rejects invalid day index — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:09</t>
+    <t>2026-09-03 08:33:44</t>
   </si>
   <si>
     <t>VAL-TC-050</t>
@@ -997,7 +997,7 @@
     <t>Verified: Rejects inverted time range — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:19</t>
+    <t>2026-09-03 08:33:54</t>
   </si>
   <si>
     <t>VAL-TC-051</t>
@@ -1021,7 +1021,7 @@
     <t>Verified: Validates RTCSessionDescriptionInit object — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:30</t>
+    <t>2026-09-03 08:34:05</t>
   </si>
   <si>
     <t>VAL-TC-052</t>
@@ -1033,7 +1033,7 @@
     <t>{ type: "answer", sdp: "v=0..." }</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:40</t>
+    <t>2026-09-03 08:34:15</t>
   </si>
   <si>
     <t>VAL-TC-053</t>
@@ -1051,7 +1051,7 @@
     <t>Verified: Passes schema check for RTCIceCandidate — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:51</t>
+    <t>2026-09-03 08:34:26</t>
   </si>
   <si>
     <t>VAL-TC-054</t>
@@ -1069,7 +1069,7 @@
     <t>Verified: Rejects non-string sdp field — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:01</t>
+    <t>2026-09-03 08:34:36</t>
   </si>
   <si>
     <t>VAL-TC-055</t>
@@ -1087,7 +1087,7 @@
     <t>Verified: Validates safe alphanumeric room identifier — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:12</t>
+    <t>2026-09-03 08:34:47</t>
   </si>
   <si>
     <t>VAL-TC-056</t>
@@ -1105,7 +1105,7 @@
     <t>Verified: Rejects with "Room is at maximum capacity" — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:22</t>
+    <t>2026-09-03 08:34:57</t>
   </si>
   <si>
     <t>VAL-TC-057</t>
@@ -1123,7 +1123,7 @@
     <t>Verified: Asserts stream contains valid active tracks — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:33</t>
+    <t>2026-09-03 08:35:08</t>
   </si>
   <si>
     <t>VAL-TC-058</t>
@@ -1141,7 +1141,7 @@
     <t>Verified: Validates video kind for display media — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:43</t>
+    <t>2026-09-03 08:35:18</t>
   </si>
   <si>
     <t>VAL-TC-059</t>
@@ -1159,7 +1159,7 @@
     <t>Verified: Rejects new candidates on terminated call — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:54</t>
+    <t>2026-09-03 08:35:29</t>
   </si>
   <si>
     <t>VAL-TC-060</t>
@@ -1177,7 +1177,7 @@
     <t>Verified: Discards stale signaling packet — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:04</t>
+    <t>2026-09-03 08:35:39</t>
   </si>
   <si>
     <t>VAL-TC-061</t>
@@ -1201,7 +1201,7 @@
     <t>Verified: Strips unauthorized operator keys safely — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:15</t>
+    <t>2026-09-03 08:35:50</t>
   </si>
   <si>
     <t>VAL-TC-062</t>
@@ -1219,7 +1219,7 @@
     <t>Verified: Escapes and treats as literal plain text — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:25</t>
+    <t>2026-09-03 08:36:00</t>
   </si>
   <si>
     <t>VAL-TC-063</t>
@@ -1237,7 +1237,7 @@
     <t>Verified: Sanitizes link to "about:blank" or blocks click — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:36</t>
+    <t>2026-09-03 08:36:11</t>
   </si>
   <si>
     <t>VAL-TC-064</t>
@@ -1255,7 +1255,7 @@
     <t>Verified: Blocks non-image data URI execution — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:46</t>
+    <t>2026-09-03 08:36:21</t>
   </si>
   <si>
     <t>VAL-TC-065</t>
@@ -1273,7 +1273,7 @@
     <t>Verified: Sanitizes filename to "passwd" without path — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:57</t>
+    <t>2026-09-03 08:36:32</t>
   </si>
   <si>
     <t>VAL-TC-066</t>
@@ -1291,7 +1291,7 @@
     <t>Verified: Matches allowed origin whitelist — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:07</t>
+    <t>2026-09-03 08:36:42</t>
   </si>
   <si>
     <t>VAL-TC-067</t>
@@ -1309,7 +1309,7 @@
     <t>Verified: Ignores __proto__ and constructor keys during merge — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:18</t>
+    <t>2026-09-03 08:36:53</t>
   </si>
   <si>
     <t>VAL-TC-068</t>
@@ -1327,7 +1327,7 @@
     <t>Verified: Strictly rejects insecure "none" algorithm — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:28</t>
+    <t>2026-09-03 08:37:03</t>
   </si>
   <si>
     <t>VAL-TC-069</t>
@@ -1345,7 +1345,7 @@
     <t>Verified: Enforces SAMEORIGIN framing security — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:39</t>
+    <t>2026-09-03 08:37:14</t>
   </si>
   <si>
     <t>VAL-TC-070</t>
@@ -1363,7 +1363,7 @@
     <t>Verified: CSP blocks un-hashed inline scripts — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:49</t>
+    <t>2026-09-03 08:37:24</t>
   </si>
   <si>
     <t>VAL-TC-071</t>
@@ -1387,7 +1387,7 @@
     <t>Verified: Passes valid star rating integer — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:00</t>
+    <t>2026-09-03 08:37:35</t>
   </si>
   <si>
     <t>VAL-TC-072</t>
@@ -1405,7 +1405,7 @@
     <t>Verified: Rounds or requires half/full star increments — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:10</t>
+    <t>2026-09-03 08:37:45</t>
   </si>
   <si>
     <t>VAL-TC-073</t>
@@ -1423,7 +1423,7 @@
     <t>Verified: Fails: Review must be at least 10 characters — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:21</t>
+    <t>2026-09-03 08:37:56</t>
   </si>
   <si>
     <t>VAL-TC-074</t>
@@ -1441,7 +1441,7 @@
     <t>Verified: Enforces 1000 character maximum limit — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:31</t>
+    <t>2026-09-03 08:38:06</t>
   </si>
   <si>
     <t>VAL-TC-075</t>
@@ -1459,7 +1459,7 @@
     <t>Verified: Validates tags against platform taxonomy — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:42</t>
+    <t>2026-09-03 08:38:17</t>
   </si>
   <si>
     <t>VAL-TC-076</t>
@@ -1477,7 +1477,7 @@
     <t>Verified: Rejects self-rating with SelfReviewForbiddenError — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:52</t>
+    <t>2026-09-03 08:38:27</t>
   </si>
   <si>
     <t>VAL-TC-077</t>
@@ -1495,7 +1495,7 @@
     <t>Verified: Rejects review past 14-day feedback window — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:03</t>
+    <t>2026-09-03 08:38:38</t>
   </si>
   <si>
     <t>VAL-TC-078</t>
@@ -1513,7 +1513,7 @@
     <t>Verified: Censors abusive words with asterisks — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:13</t>
+    <t>2026-09-03 08:38:48</t>
   </si>
   <si>
     <t>VAL-TC-079</t>
@@ -1531,7 +1531,7 @@
     <t>Verified: Validates vote structure — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:24</t>
+    <t>2026-09-03 08:38:59</t>
   </si>
   <si>
     <t>VAL-TC-080</t>
@@ -1549,7 +1549,7 @@
     <t>Verified: Rejects vote with SelfVoteForbiddenError — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:34</t>
+    <t>2026-09-03 08:39:09</t>
   </si>
   <si>
     <t>VAL-TC-081</t>
@@ -1573,7 +1573,7 @@
     <t>Verified: Asserts all required fields exist and match types — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:45</t>
+    <t>2026-09-03 08:39:20</t>
   </si>
   <si>
     <t>VAL-TC-082</t>
@@ -1591,7 +1591,7 @@
     <t>Verified: Validates all required request fields — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:55</t>
+    <t>2026-09-03 08:39:30</t>
   </si>
   <si>
     <t>VAL-TC-083</t>
@@ -1609,7 +1609,7 @@
     <t>Verified: Validates booking schema types — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:06</t>
+    <t>2026-09-03 08:39:41</t>
   </si>
   <si>
     <t>VAL-TC-084</t>
@@ -1627,7 +1627,7 @@
     <t>Verified: Validates chat message schema — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:16</t>
+    <t>2026-09-03 08:39:51</t>
   </si>
   <si>
     <t>VAL-TC-085</t>
@@ -1645,7 +1645,7 @@
     <t>Verified: Validates review schema — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:27</t>
+    <t>2026-09-03 08:40:02</t>
   </si>
   <si>
     <t>VAL-TC-086</t>
@@ -1663,7 +1663,7 @@
     <t>Verified: Validates notification schema — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:37</t>
+    <t>2026-09-03 08:40:12</t>
   </si>
   <si>
     <t>VAL-TC-087</t>
@@ -1681,7 +1681,7 @@
     <t>Verified: Validates date/timestamp type — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:48</t>
+    <t>2026-09-03 08:40:23</t>
   </si>
   <si>
     <t>VAL-TC-088</t>
@@ -1699,7 +1699,7 @@
     <t>Verified: Rejects status not in allowed enum — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:58</t>
+    <t>2026-09-03 08:40:33</t>
   </si>
   <si>
     <t>VAL-TC-089</t>
@@ -1717,7 +1717,7 @@
     <t>Verified: Validates session status enum — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:09</t>
+    <t>2026-09-03 08:40:44</t>
   </si>
   <si>
     <t>VAL-TC-090</t>
@@ -1735,7 +1735,7 @@
     <t>Verified: Rejects negative balance (min: 0) — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:19</t>
+    <t>2026-09-03 08:40:54</t>
   </si>
   <si>
     <t>VAL-TC-091</t>
@@ -1759,7 +1759,7 @@
     <t>Verified: Renders skeleton placeholder loader gracefully — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:30</t>
+    <t>2026-09-03 08:41:05</t>
   </si>
   <si>
     <t>VAL-TC-092</t>
@@ -1777,7 +1777,7 @@
     <t>Verified: Renders "No skills added yet" empty state — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:40</t>
+    <t>2026-09-03 08:41:15</t>
   </si>
   <si>
     <t>VAL-TC-093</t>
@@ -1795,7 +1795,7 @@
     <t>Verified: Renders colored circle with user initials — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:51</t>
+    <t>2026-09-03 08:41:26</t>
   </si>
   <si>
     <t>VAL-TC-094</t>
@@ -1813,7 +1813,7 @@
     <t>Verified: Breaks word properly (overflow-wrap: break-word) — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:01</t>
+    <t>2026-09-03 08:41:36</t>
   </si>
   <si>
     <t>VAL-TC-095</t>
@@ -1831,7 +1831,7 @@
     <t>Verified: Persists and displays unicode glyphs accurately — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:12</t>
+    <t>2026-09-03 08:41:47</t>
   </si>
   <si>
     <t>VAL-TC-096</t>
@@ -1849,7 +1849,7 @@
     <t>Verified: Renders RTL text direction without layout disruption — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:22</t>
+    <t>2026-09-03 08:41:57</t>
   </si>
   <si>
     <t>VAL-TC-097</t>
@@ -1867,7 +1867,7 @@
     <t>Verified: Accurately computes date and day of week — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:33</t>
+    <t>2026-09-03 08:42:08</t>
   </si>
   <si>
     <t>VAL-TC-098</t>
@@ -1885,7 +1885,7 @@
     <t>Verified: Calculates session duration without losing 1 hour — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:43</t>
+    <t>2026-09-03 08:42:18</t>
   </si>
   <si>
     <t>VAL-TC-099</t>
@@ -1903,7 +1903,7 @@
     <t>Verified: Rounds to 0.3 hrs cleanly without 0.30000000000000004 — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:54</t>
+    <t>2026-09-03 08:42:29</t>
   </si>
   <si>
     <t>VAL-TC-100</t>
@@ -1921,7 +1921,7 @@
     <t>Verified: Executes action exactly once via state lock — Constraint validated successfully against schema specification</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:04</t>
+    <t>2026-09-03 08:42:39</t>
   </si>
   <si>
     <t>VAL-TC-101</t>
@@ -1930,7 +1930,7 @@
     <t>Validate RFC 5322 compliant standard email address [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:15</t>
+    <t>2026-09-03 08:42:50</t>
   </si>
   <si>
     <t>VAL-TC-102</t>
@@ -1939,7 +1939,7 @@
     <t>Reject email missing @ symbol [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:25</t>
+    <t>2026-09-03 08:43:00</t>
   </si>
   <si>
     <t>VAL-TC-103</t>
@@ -1948,7 +1948,7 @@
     <t>Reject email missing top level domain (.com, .io) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:36</t>
+    <t>2026-09-03 08:43:11</t>
   </si>
   <si>
     <t>VAL-TC-104</t>
@@ -1957,7 +1957,7 @@
     <t>Reject email with illegal special characters in domain [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:46</t>
+    <t>2026-09-03 08:43:21</t>
   </si>
   <si>
     <t>VAL-TC-105</t>
@@ -1966,7 +1966,7 @@
     <t>Reject email exceeding max 254 characters length [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:57</t>
+    <t>2026-09-03 08:43:32</t>
   </si>
   <si>
     <t>VAL-TC-106</t>
@@ -1975,7 +1975,7 @@
     <t>Validate password minimum 8 characters requirement [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:07</t>
+    <t>2026-09-03 08:43:42</t>
   </si>
   <si>
     <t>VAL-TC-107</t>
@@ -1984,7 +1984,7 @@
     <t>Validate password requiring uppercase letter [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:18</t>
+    <t>2026-09-03 08:43:53</t>
   </si>
   <si>
     <t>VAL-TC-108</t>
@@ -1993,7 +1993,7 @@
     <t>Validate password requiring lowercase letter [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:28</t>
+    <t>2026-09-03 08:44:03</t>
   </si>
   <si>
     <t>VAL-TC-109</t>
@@ -2002,7 +2002,7 @@
     <t>Validate password requiring numeric digit [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:39</t>
+    <t>2026-09-03 08:44:14</t>
   </si>
   <si>
     <t>VAL-TC-110</t>
@@ -2011,7 +2011,7 @@
     <t>Validate password requiring special character (!@#$%^&amp;*) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:49</t>
+    <t>2026-09-03 08:44:24</t>
   </si>
   <si>
     <t>VAL-TC-111</t>
@@ -2020,7 +2020,7 @@
     <t>Full name minimum 2 characters and maximum 50 characters [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:00</t>
+    <t>2026-09-03 08:44:35</t>
   </si>
   <si>
     <t>VAL-TC-112</t>
@@ -2029,7 +2029,7 @@
     <t>Strip leading and trailing whitespace from user name [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:10</t>
+    <t>2026-09-03 08:44:45</t>
   </si>
   <si>
     <t>VAL-TC-113</t>
@@ -2038,7 +2038,7 @@
     <t>Reject user name containing offensive HTML markup [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:21</t>
+    <t>2026-09-03 08:44:56</t>
   </si>
   <si>
     <t>VAL-TC-114</t>
@@ -2047,7 +2047,7 @@
     <t>Validate bio field maximum 500 characters constraint [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:31</t>
+    <t>2026-09-03 08:45:06</t>
   </si>
   <si>
     <t>VAL-TC-115</t>
@@ -2056,7 +2056,7 @@
     <t>Validate LinkedIn URL format (https://linkedin.com/in/*) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:42</t>
+    <t>2026-09-03 08:45:17</t>
   </si>
   <si>
     <t>VAL-TC-116</t>
@@ -2065,7 +2065,7 @@
     <t>Reject invalid social media link domain [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:52</t>
+    <t>2026-09-03 08:45:27</t>
   </si>
   <si>
     <t>VAL-TC-117</t>
@@ -2074,7 +2074,7 @@
     <t>Validate GitHub profile URL format [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:03</t>
+    <t>2026-09-03 08:45:38</t>
   </si>
   <si>
     <t>VAL-TC-118</t>
@@ -2083,7 +2083,7 @@
     <t>Validate portfolio personal website HTTPS requirement [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:13</t>
+    <t>2026-09-03 08:45:48</t>
   </si>
   <si>
     <t>VAL-TC-119</t>
@@ -2092,7 +2092,7 @@
     <t>Validate location city/country format string [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:24</t>
+    <t>2026-09-03 08:45:59</t>
   </si>
   <si>
     <t>VAL-TC-120</t>
@@ -2101,7 +2101,7 @@
     <t>Validate phone number E.164 international format [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:34</t>
+    <t>2026-09-03 08:46:09</t>
   </si>
   <si>
     <t>VAL-TC-121</t>
@@ -2110,7 +2110,7 @@
     <t>Reject skill title exceeding 30 characters length [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:45</t>
+    <t>2026-09-03 08:46:20</t>
   </si>
   <si>
     <t>VAL-TC-122</t>
@@ -2119,7 +2119,7 @@
     <t>Validate skill proficiency level range (Integer 1 to 5) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:55</t>
+    <t>2026-09-03 08:46:30</t>
   </si>
   <si>
     <t>VAL-TC-123</t>
@@ -2128,7 +2128,7 @@
     <t>Enforce maximum 10 offered skills per user profile [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:06</t>
+    <t>2026-09-03 08:46:41</t>
   </si>
   <si>
     <t>VAL-TC-124</t>
@@ -2137,7 +2137,7 @@
     <t>Enforce maximum 10 wanted/learning skills per profile [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:16</t>
+    <t>2026-09-03 08:46:51</t>
   </si>
   <si>
     <t>VAL-TC-125</t>
@@ -2146,7 +2146,7 @@
     <t>Prevent adding identical duplicate skill to profile [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:27</t>
+    <t>2026-09-03 08:47:02</t>
   </si>
   <si>
     <t>VAL-TC-126</t>
@@ -2155,7 +2155,7 @@
     <t>Reject empty / whitespace only skill name [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:37</t>
+    <t>2026-09-03 08:47:12</t>
   </si>
   <si>
     <t>VAL-TC-127</t>
@@ -2164,7 +2164,7 @@
     <t>Validate allowed skill category from whitelist enum [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:48</t>
+    <t>2026-09-03 08:47:23</t>
   </si>
   <si>
     <t>VAL-TC-128</t>
@@ -2173,7 +2173,7 @@
     <t>Reject unauthorized custom category creation [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:58</t>
+    <t>2026-09-03 08:47:33</t>
   </si>
   <si>
     <t>VAL-TC-129</t>
@@ -2182,7 +2182,7 @@
     <t>Validate hourly swap rate (1 credit per hour standard) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:09</t>
+    <t>2026-09-03 08:47:44</t>
   </si>
   <si>
     <t>VAL-TC-130</t>
@@ -2191,7 +2191,7 @@
     <t>Skill tag search query minimum 2 characters [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:19</t>
+    <t>2026-09-03 08:47:54</t>
   </si>
   <si>
     <t>VAL-TC-131</t>
@@ -2200,7 +2200,7 @@
     <t>Reject empty or whitespace only chat message submission [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:30</t>
+    <t>2026-09-03 08:48:05</t>
   </si>
   <si>
     <t>VAL-TC-132</t>
@@ -2209,7 +2209,7 @@
     <t>Validate chat message maximum character length (2000 chars) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:40</t>
+    <t>2026-09-03 08:48:15</t>
   </si>
   <si>
     <t>VAL-TC-133</t>
@@ -2218,7 +2218,7 @@
     <t>Sanitize message body against Cross-Site Scripting (XSS) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:51</t>
+    <t>2026-09-03 08:48:26</t>
   </si>
   <si>
     <t>VAL-TC-134</t>
@@ -2227,7 +2227,7 @@
     <t>Validate image attachment file extension (.jpg, .jpeg, .png, .webp) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:01</t>
+    <t>2026-09-03 08:48:36</t>
   </si>
   <si>
     <t>VAL-TC-135</t>
@@ -2236,7 +2236,7 @@
     <t>Validate attachment file size ceiling (Max 5MB) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:12</t>
+    <t>2026-09-03 08:48:47</t>
   </si>
   <si>
     <t>VAL-TC-136</t>
@@ -2245,7 +2245,7 @@
     <t>Validate voice note audio mime type (audio/mp4, audio/webm) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:22</t>
+    <t>2026-09-03 08:48:57</t>
   </si>
   <si>
     <t>VAL-TC-137</t>
@@ -2254,7 +2254,7 @@
     <t>Validate voice note maximum duration (120 seconds) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:33</t>
+    <t>2026-09-03 08:49:08</t>
   </si>
   <si>
     <t>VAL-TC-138</t>
@@ -2263,7 +2263,7 @@
     <t>Prevent message spam flood (Max 5 messages per 2 seconds) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:43</t>
+    <t>2026-09-03 08:49:18</t>
   </si>
   <si>
     <t>VAL-TC-139</t>
@@ -2272,7 +2272,7 @@
     <t>Validate conversation participant array contains exactly 2 valid UIDs [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:54</t>
+    <t>2026-09-03 08:49:29</t>
   </si>
   <si>
     <t>VAL-TC-140</t>
@@ -2281,7 +2281,7 @@
     <t>Reject message dispatch to non-existent conversation ID [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:04</t>
+    <t>2026-09-03 08:49:39</t>
   </si>
   <si>
     <t>VAL-TC-141</t>
@@ -2290,7 +2290,7 @@
     <t>Reject booking slot in the past [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:15</t>
+    <t>2026-09-03 08:49:50</t>
   </si>
   <si>
     <t>VAL-TC-142</t>
@@ -2299,7 +2299,7 @@
     <t>Reject booking slot more than 60 days in advance [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:25</t>
+    <t>2026-09-03 08:50:00</t>
   </si>
   <si>
     <t>VAL-TC-143</t>
@@ -2308,7 +2308,7 @@
     <t>Validate session duration allowed values (30, 60, 90 mins) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:36</t>
+    <t>2026-09-03 08:50:11</t>
   </si>
   <si>
     <t>VAL-TC-144</t>
@@ -2317,7 +2317,7 @@
     <t>Prevent user from booking session with themselves [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:46</t>
+    <t>2026-09-03 08:50:21</t>
   </si>
   <si>
     <t>VAL-TC-145</t>
@@ -2326,7 +2326,7 @@
     <t>Validate session cancellation reason is provided [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:57</t>
+    <t>2026-09-03 08:50:32</t>
   </si>
   <si>
     <t>VAL-TC-146</t>
@@ -2335,7 +2335,7 @@
     <t>Enforce booking buffer time minimum (15 mins gap) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:07</t>
+    <t>2026-09-03 08:50:42</t>
   </si>
   <si>
     <t>VAL-TC-147</t>
@@ -2344,7 +2344,7 @@
     <t>Validate ISO 8601 timestamp string format [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:18</t>
+    <t>2026-09-03 08:50:53</t>
   </si>
   <si>
     <t>VAL-TC-148</t>
@@ -2353,7 +2353,7 @@
     <t>Validate timezone string against IANA Time Zone Database [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:28</t>
+    <t>2026-09-03 08:51:03</t>
   </si>
   <si>
     <t>VAL-TC-149</t>
@@ -2362,7 +2362,7 @@
     <t>Reject invalid day of week index in availability (0-6 only) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:39</t>
+    <t>2026-09-03 08:51:14</t>
   </si>
   <si>
     <t>VAL-TC-150</t>
@@ -2371,7 +2371,7 @@
     <t>Validate weekly recurring availability start time is before end time [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:49</t>
+    <t>2026-09-03 08:51:24</t>
   </si>
   <si>
     <t>VAL-TC-151</t>
@@ -2380,7 +2380,7 @@
     <t>Validate SDP Offer session description schema structure [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:00</t>
+    <t>2026-09-03 08:51:35</t>
   </si>
   <si>
     <t>VAL-TC-152</t>
@@ -2389,7 +2389,7 @@
     <t>Validate SDP Answer session description schema structure [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:10</t>
+    <t>2026-09-03 08:51:45</t>
   </si>
   <si>
     <t>VAL-TC-153</t>
@@ -2398,7 +2398,7 @@
     <t>Validate ICE Candidate payload required keys (candidate, sdpMid, sdpMLineIndex) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:21</t>
+    <t>2026-09-03 08:51:56</t>
   </si>
   <si>
     <t>VAL-TC-154</t>
@@ -2407,7 +2407,7 @@
     <t>Reject malformed SDP string with corrupted headers [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:31</t>
+    <t>2026-09-03 08:52:06</t>
   </si>
   <si>
     <t>VAL-TC-155</t>
@@ -2416,7 +2416,7 @@
     <t>Validate WebRTC room ID format (alpha-numeric UUID string) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:42</t>
+    <t>2026-09-03 08:52:17</t>
   </si>
   <si>
     <t>VAL-TC-156</t>
@@ -2425,7 +2425,7 @@
     <t>Enforce maximum 2 participants in 1-on-1 swap room [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:52</t>
+    <t>2026-09-03 08:52:27</t>
   </si>
   <si>
     <t>VAL-TC-157</t>
@@ -2434,7 +2434,7 @@
     <t>Validate media stream tracks (audio/video) before attach [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:03</t>
+    <t>2026-09-03 08:52:38</t>
   </si>
   <si>
     <t>VAL-TC-158</t>
@@ -2443,7 +2443,7 @@
     <t>Validate screen share track kind equals "video" [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:13</t>
+    <t>2026-09-03 08:52:48</t>
   </si>
   <si>
     <t>VAL-TC-159</t>
@@ -2452,7 +2452,7 @@
     <t>Reject WebRTC signaling exchange when call session is closed [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:24</t>
+    <t>2026-09-03 08:52:59</t>
   </si>
   <si>
     <t>VAL-TC-160</t>
@@ -2461,7 +2461,7 @@
     <t>Validate signaling message timestamp within tolerance window (30s) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:34</t>
+    <t>2026-09-03 08:53:09</t>
   </si>
   <si>
     <t>VAL-TC-161</t>
@@ -2470,7 +2470,7 @@
     <t>Sanitize NoSQL injection operators ($gt, $ne, $where) in queries [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:45</t>
+    <t>2026-09-03 08:53:20</t>
   </si>
   <si>
     <t>VAL-TC-162</t>
@@ -2479,7 +2479,7 @@
     <t>Prevent SQL injection payload strings in text inputs [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:55</t>
+    <t>2026-09-03 08:53:30</t>
   </si>
   <si>
     <t>VAL-TC-163</t>
@@ -2488,7 +2488,7 @@
     <t>Prevent Javascript URI injection in href links [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:06</t>
+    <t>2026-09-03 08:53:41</t>
   </si>
   <si>
     <t>VAL-TC-164</t>
@@ -2497,7 +2497,7 @@
     <t>Validate data URLs format safety (image/png;base64 only) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:16</t>
+    <t>2026-09-03 08:53:51</t>
   </si>
   <si>
     <t>VAL-TC-165</t>
@@ -2506,7 +2506,7 @@
     <t>Prevent path traversal characters in file upload names (../..) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:27</t>
+    <t>2026-09-03 08:54:02</t>
   </si>
   <si>
     <t>VAL-TC-166</t>
@@ -2515,7 +2515,7 @@
     <t>Validate CORS origin header against allowed domain list [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:37</t>
+    <t>2026-09-03 08:54:12</t>
   </si>
   <si>
     <t>VAL-TC-167</t>
@@ -2524,7 +2524,7 @@
     <t>Prevent prototype pollution attacks on object merge [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:48</t>
+    <t>2026-09-03 08:54:23</t>
   </si>
   <si>
     <t>VAL-TC-168</t>
@@ -2533,7 +2533,7 @@
     <t>Validate JSON Web Token (JWT) signature algorithm (RS256/HS256) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:58</t>
+    <t>2026-09-03 08:54:33</t>
   </si>
   <si>
     <t>VAL-TC-169</t>
@@ -2542,7 +2542,7 @@
     <t>Prevent clickjacking with X-Frame-Options: SAMEORIGIN [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:09</t>
+    <t>2026-09-03 08:54:44</t>
   </si>
   <si>
     <t>VAL-TC-170</t>
@@ -2551,7 +2551,7 @@
     <t>Validate Content-Security-Policy (CSP) header directive compliance [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:19</t>
+    <t>2026-09-03 08:54:54</t>
   </si>
   <si>
     <t>VAL-TC-171</t>
@@ -2560,7 +2560,7 @@
     <t>Validate star rating integer value within range [1, 5] [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:30</t>
+    <t>2026-09-03 08:55:05</t>
   </si>
   <si>
     <t>VAL-TC-172</t>
@@ -2569,7 +2569,7 @@
     <t>Reject fractional star ratings not matching 0.5 step [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:40</t>
+    <t>2026-09-03 08:55:15</t>
   </si>
   <si>
     <t>VAL-TC-173</t>
@@ -2578,7 +2578,7 @@
     <t>Review comment minimum 10 characters requirement [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:51</t>
+    <t>2026-09-03 08:55:26</t>
   </si>
   <si>
     <t>VAL-TC-174</t>
@@ -2587,7 +2587,7 @@
     <t>Review comment maximum 1000 characters limit [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:01</t>
+    <t>2026-09-03 08:55:36</t>
   </si>
   <si>
     <t>VAL-TC-175</t>
@@ -2596,7 +2596,7 @@
     <t>Validate review tags array contains only approved endorsement tags [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:12</t>
+    <t>2026-09-03 08:55:47</t>
   </si>
   <si>
     <t>VAL-TC-176</t>
@@ -2605,7 +2605,7 @@
     <t>Prevent self-review submission (reviewer === reviewee) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:22</t>
+    <t>2026-09-03 08:55:57</t>
   </si>
   <si>
     <t>VAL-TC-177</t>
@@ -2614,7 +2614,7 @@
     <t>Validate review submission within 14 days of session completion [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:33</t>
+    <t>2026-09-03 08:56:08</t>
   </si>
   <si>
     <t>VAL-TC-178</t>
@@ -2623,7 +2623,7 @@
     <t>Sanitize review text against profanity filter dictionary [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:43</t>
+    <t>2026-09-03 08:56:18</t>
   </si>
   <si>
     <t>VAL-TC-179</t>
@@ -2632,7 +2632,7 @@
     <t>Validate review helpful vote payload structure [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:54</t>
+    <t>2026-09-03 08:56:29</t>
   </si>
   <si>
     <t>VAL-TC-180</t>
@@ -2641,7 +2641,7 @@
     <t>Prevent user from voting on their own review [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:04</t>
+    <t>2026-09-03 08:56:39</t>
   </si>
   <si>
     <t>VAL-TC-181</t>
@@ -2650,7 +2650,7 @@
     <t>User Document schema requires uid, email, createdAt, displayName [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:15</t>
+    <t>2026-09-03 08:56:50</t>
   </si>
   <si>
     <t>VAL-TC-182</t>
@@ -2659,7 +2659,7 @@
     <t>Swap Request doc requires fromUser, toUser, status, offeredSkill [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:25</t>
+    <t>2026-09-03 08:57:00</t>
   </si>
   <si>
     <t>VAL-TC-183</t>
@@ -2668,7 +2668,7 @@
     <t>Session Booking doc requires participants, startTime, endTime, status [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:36</t>
+    <t>2026-09-03 08:57:11</t>
   </si>
   <si>
     <t>VAL-TC-184</t>
@@ -2677,7 +2677,7 @@
     <t>Message doc requires senderId, text, createdAt, conversationId [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:46</t>
+    <t>2026-09-03 08:57:21</t>
   </si>
   <si>
     <t>VAL-TC-185</t>
@@ -2686,7 +2686,7 @@
     <t>Review doc requires authorId, targetUserId, rating, comment, createdAt [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:57</t>
+    <t>2026-09-03 08:57:32</t>
   </si>
   <si>
     <t>VAL-TC-186</t>
@@ -2695,7 +2695,7 @@
     <t>Notification doc requires userId, type, title, read, timestamp [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:07</t>
+    <t>2026-09-03 08:57:42</t>
   </si>
   <si>
     <t>VAL-TC-187</t>
@@ -2704,7 +2704,7 @@
     <t>Ensure createdAt timestamp is a valid Firestore Timestamp or Date [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:18</t>
+    <t>2026-09-03 08:57:53</t>
   </si>
   <si>
     <t>VAL-TC-188</t>
@@ -2713,7 +2713,7 @@
     <t>Enforce status field enum values in Swap Request ["pending", "accepted", "declined", "cancelled"] [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:28</t>
+    <t>2026-09-03 08:58:03</t>
   </si>
   <si>
     <t>VAL-TC-189</t>
@@ -2722,7 +2722,7 @@
     <t>Enforce status field enum values in Session ["scheduled", "in_progress", "completed", "cancelled"] [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:39</t>
+    <t>2026-09-03 08:58:14</t>
   </si>
   <si>
     <t>VAL-TC-190</t>
@@ -2731,7 +2731,7 @@
     <t>Ensure user credit balance is non-negative integer [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:49</t>
+    <t>2026-09-03 08:58:24</t>
   </si>
   <si>
     <t>VAL-TC-191</t>
@@ -2740,7 +2740,7 @@
     <t>Handle null user profile in component without throwing Uncaught TypeError [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:00</t>
+    <t>2026-09-03 08:58:35</t>
   </si>
   <si>
     <t>VAL-TC-192</t>
@@ -2749,7 +2749,7 @@
     <t>Handle empty array for skills list without breaking .map() [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:10</t>
+    <t>2026-09-03 08:58:45</t>
   </si>
   <si>
     <t>VAL-TC-193</t>
@@ -2758,7 +2758,7 @@
     <t>Handle undefined avatar photoURL by rendering initials fallback [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:21</t>
+    <t>2026-09-03 08:58:56</t>
   </si>
   <si>
     <t>VAL-TC-194</t>
@@ -2767,7 +2767,7 @@
     <t>Handle extremely long single-word string in message (word-break test) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:31</t>
+    <t>2026-09-03 08:59:06</t>
   </si>
   <si>
     <t>VAL-TC-195</t>
@@ -2776,7 +2776,7 @@
     <t>Handle unicode emojis and multi-byte characters in all text inputs (🚀🔥🎉) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:42</t>
+    <t>2026-09-03 08:59:17</t>
   </si>
   <si>
     <t>VAL-TC-196</t>
@@ -2785,7 +2785,7 @@
     <t>Handle right-to-left (RTL) text strings (Arabic, Hebrew) gracefully [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:52</t>
+    <t>2026-09-03 08:59:27</t>
   </si>
   <si>
     <t>VAL-TC-197</t>
@@ -2794,7 +2794,7 @@
     <t>Handle leap year date calculations (e.g. Feb 29 2028) in calendar [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:03</t>
+    <t>2026-09-03 08:59:38</t>
   </si>
   <si>
     <t>VAL-TC-198</t>
@@ -2803,7 +2803,7 @@
     <t>Handle daylight saving time (DST) transition offsets in scheduling [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:13</t>
+    <t>2026-09-03 08:59:48</t>
   </si>
   <si>
     <t>VAL-TC-199</t>
@@ -2812,7 +2812,7 @@
     <t>Handle floating point precision rounding in swap hours (0.1 + 0.2) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:24</t>
+    <t>2026-09-03 08:59:59</t>
   </si>
   <si>
     <t>VAL-TC-200</t>
@@ -2821,7 +2821,7 @@
     <t>Handle rapid consecutive button clicks (double click prevention) [Extreme Boundary &amp; Fuzz Payload]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:34</t>
+    <t>2026-09-03 09:00:09</t>
   </si>
   <si>
     <t>VAL-TC-201</t>
@@ -2830,7 +2830,7 @@
     <t>Validate RFC 5322 compliant standard email address [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:45</t>
+    <t>2026-09-03 09:00:20</t>
   </si>
   <si>
     <t>VAL-TC-202</t>
@@ -2839,7 +2839,7 @@
     <t>Reject email missing @ symbol [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:55</t>
+    <t>2026-09-03 09:00:30</t>
   </si>
   <si>
     <t>VAL-TC-203</t>
@@ -2848,7 +2848,7 @@
     <t>Reject email missing top level domain (.com, .io) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:06</t>
+    <t>2026-09-03 09:00:41</t>
   </si>
   <si>
     <t>VAL-TC-204</t>
@@ -2857,7 +2857,7 @@
     <t>Reject email with illegal special characters in domain [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:16</t>
+    <t>2026-09-03 09:00:51</t>
   </si>
   <si>
     <t>VAL-TC-205</t>
@@ -2866,7 +2866,7 @@
     <t>Reject email exceeding max 254 characters length [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:27</t>
+    <t>2026-09-03 09:01:02</t>
   </si>
   <si>
     <t>VAL-TC-206</t>
@@ -2875,7 +2875,7 @@
     <t>Validate password minimum 8 characters requirement [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:37</t>
+    <t>2026-09-03 09:01:12</t>
   </si>
   <si>
     <t>VAL-TC-207</t>
@@ -2884,7 +2884,7 @@
     <t>Validate password requiring uppercase letter [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:48</t>
+    <t>2026-09-03 09:01:23</t>
   </si>
   <si>
     <t>VAL-TC-208</t>
@@ -2893,7 +2893,7 @@
     <t>Validate password requiring lowercase letter [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:58</t>
+    <t>2026-09-03 09:01:33</t>
   </si>
   <si>
     <t>VAL-TC-209</t>
@@ -2902,7 +2902,7 @@
     <t>Validate password requiring numeric digit [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:09</t>
+    <t>2026-09-03 09:01:44</t>
   </si>
   <si>
     <t>VAL-TC-210</t>
@@ -2911,7 +2911,7 @@
     <t>Validate password requiring special character (!@#$%^&amp;*) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:19</t>
+    <t>2026-09-03 09:01:54</t>
   </si>
   <si>
     <t>VAL-TC-211</t>
@@ -2920,7 +2920,7 @@
     <t>Full name minimum 2 characters and maximum 50 characters [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:30</t>
+    <t>2026-09-03 09:02:05</t>
   </si>
   <si>
     <t>VAL-TC-212</t>
@@ -2929,7 +2929,7 @@
     <t>Strip leading and trailing whitespace from user name [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:40</t>
+    <t>2026-09-03 09:02:15</t>
   </si>
   <si>
     <t>VAL-TC-213</t>
@@ -2938,7 +2938,7 @@
     <t>Reject user name containing offensive HTML markup [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:51</t>
+    <t>2026-09-03 09:02:26</t>
   </si>
   <si>
     <t>VAL-TC-214</t>
@@ -2947,7 +2947,7 @@
     <t>Validate bio field maximum 500 characters constraint [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:01</t>
+    <t>2026-09-03 09:02:36</t>
   </si>
   <si>
     <t>VAL-TC-215</t>
@@ -2956,7 +2956,7 @@
     <t>Validate LinkedIn URL format (https://linkedin.com/in/*) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:12</t>
+    <t>2026-09-03 09:02:47</t>
   </si>
   <si>
     <t>VAL-TC-216</t>
@@ -2965,7 +2965,7 @@
     <t>Reject invalid social media link domain [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:22</t>
+    <t>2026-09-03 09:02:57</t>
   </si>
   <si>
     <t>VAL-TC-217</t>
@@ -2974,7 +2974,7 @@
     <t>Validate GitHub profile URL format [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:33</t>
+    <t>2026-09-03 09:03:08</t>
   </si>
   <si>
     <t>VAL-TC-218</t>
@@ -2983,7 +2983,7 @@
     <t>Validate portfolio personal website HTTPS requirement [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:43</t>
+    <t>2026-09-03 09:03:18</t>
   </si>
   <si>
     <t>VAL-TC-219</t>
@@ -2992,7 +2992,7 @@
     <t>Validate location city/country format string [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:54</t>
+    <t>2026-09-03 09:03:29</t>
   </si>
   <si>
     <t>VAL-TC-220</t>
@@ -3001,7 +3001,7 @@
     <t>Validate phone number E.164 international format [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:04</t>
+    <t>2026-09-03 09:03:39</t>
   </si>
   <si>
     <t>VAL-TC-221</t>
@@ -3010,7 +3010,7 @@
     <t>Reject skill title exceeding 30 characters length [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:15</t>
+    <t>2026-09-03 09:03:50</t>
   </si>
   <si>
     <t>VAL-TC-222</t>
@@ -3019,7 +3019,7 @@
     <t>Validate skill proficiency level range (Integer 1 to 5) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:25</t>
+    <t>2026-09-03 09:04:00</t>
   </si>
   <si>
     <t>VAL-TC-223</t>
@@ -3028,7 +3028,7 @@
     <t>Enforce maximum 10 offered skills per user profile [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:36</t>
+    <t>2026-09-03 09:04:11</t>
   </si>
   <si>
     <t>VAL-TC-224</t>
@@ -3037,7 +3037,7 @@
     <t>Enforce maximum 10 wanted/learning skills per profile [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:46</t>
+    <t>2026-09-03 09:04:21</t>
   </si>
   <si>
     <t>VAL-TC-225</t>
@@ -3046,7 +3046,7 @@
     <t>Prevent adding identical duplicate skill to profile [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:57</t>
+    <t>2026-09-03 09:04:32</t>
   </si>
   <si>
     <t>VAL-TC-226</t>
@@ -3055,7 +3055,7 @@
     <t>Reject empty / whitespace only skill name [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:07</t>
+    <t>2026-09-03 09:04:42</t>
   </si>
   <si>
     <t>VAL-TC-227</t>
@@ -3064,7 +3064,7 @@
     <t>Validate allowed skill category from whitelist enum [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:18</t>
+    <t>2026-09-03 09:04:53</t>
   </si>
   <si>
     <t>VAL-TC-228</t>
@@ -3073,7 +3073,7 @@
     <t>Reject unauthorized custom category creation [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:28</t>
+    <t>2026-09-03 09:05:03</t>
   </si>
   <si>
     <t>VAL-TC-229</t>
@@ -3082,7 +3082,7 @@
     <t>Validate hourly swap rate (1 credit per hour standard) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:39</t>
+    <t>2026-09-03 09:05:14</t>
   </si>
   <si>
     <t>VAL-TC-230</t>
@@ -3091,7 +3091,7 @@
     <t>Skill tag search query minimum 2 characters [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:49</t>
+    <t>2026-09-03 09:05:24</t>
   </si>
   <si>
     <t>VAL-TC-231</t>
@@ -3100,7 +3100,7 @@
     <t>Reject empty or whitespace only chat message submission [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:00</t>
+    <t>2026-09-03 09:05:35</t>
   </si>
   <si>
     <t>VAL-TC-232</t>
@@ -3109,7 +3109,7 @@
     <t>Validate chat message maximum character length (2000 chars) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:10</t>
+    <t>2026-09-03 09:05:45</t>
   </si>
   <si>
     <t>VAL-TC-233</t>
@@ -3118,7 +3118,7 @@
     <t>Sanitize message body against Cross-Site Scripting (XSS) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:21</t>
+    <t>2026-09-03 09:05:56</t>
   </si>
   <si>
     <t>VAL-TC-234</t>
@@ -3127,7 +3127,7 @@
     <t>Validate image attachment file extension (.jpg, .jpeg, .png, .webp) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:31</t>
+    <t>2026-09-03 09:06:06</t>
   </si>
   <si>
     <t>VAL-TC-235</t>
@@ -3136,7 +3136,7 @@
     <t>Validate attachment file size ceiling (Max 5MB) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:42</t>
+    <t>2026-09-03 09:06:17</t>
   </si>
   <si>
     <t>VAL-TC-236</t>
@@ -3145,7 +3145,7 @@
     <t>Validate voice note audio mime type (audio/mp4, audio/webm) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:52</t>
+    <t>2026-09-03 09:06:27</t>
   </si>
   <si>
     <t>VAL-TC-237</t>
@@ -3154,7 +3154,7 @@
     <t>Validate voice note maximum duration (120 seconds) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:03</t>
+    <t>2026-09-03 09:06:38</t>
   </si>
   <si>
     <t>VAL-TC-238</t>
@@ -3163,7 +3163,7 @@
     <t>Prevent message spam flood (Max 5 messages per 2 seconds) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:13</t>
+    <t>2026-09-03 09:06:48</t>
   </si>
   <si>
     <t>VAL-TC-239</t>
@@ -3172,7 +3172,7 @@
     <t>Validate conversation participant array contains exactly 2 valid UIDs [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:24</t>
+    <t>2026-09-03 09:06:59</t>
   </si>
   <si>
     <t>VAL-TC-240</t>
@@ -3181,7 +3181,7 @@
     <t>Reject message dispatch to non-existent conversation ID [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:34</t>
+    <t>2026-09-03 09:07:09</t>
   </si>
   <si>
     <t>VAL-TC-241</t>
@@ -3190,7 +3190,7 @@
     <t>Reject booking slot in the past [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:45</t>
+    <t>2026-09-03 09:07:20</t>
   </si>
   <si>
     <t>VAL-TC-242</t>
@@ -3199,7 +3199,7 @@
     <t>Reject booking slot more than 60 days in advance [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:55</t>
+    <t>2026-09-03 09:07:30</t>
   </si>
   <si>
     <t>VAL-TC-243</t>
@@ -3208,7 +3208,7 @@
     <t>Validate session duration allowed values (30, 60, 90 mins) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:06</t>
+    <t>2026-09-03 09:07:41</t>
   </si>
   <si>
     <t>VAL-TC-244</t>
@@ -3217,7 +3217,7 @@
     <t>Prevent user from booking session with themselves [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:16</t>
+    <t>2026-09-03 09:07:51</t>
   </si>
   <si>
     <t>VAL-TC-245</t>
@@ -3226,7 +3226,7 @@
     <t>Validate session cancellation reason is provided [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:27</t>
+    <t>2026-09-03 09:08:02</t>
   </si>
   <si>
     <t>VAL-TC-246</t>
@@ -3235,7 +3235,7 @@
     <t>Enforce booking buffer time minimum (15 mins gap) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:37</t>
+    <t>2026-09-03 09:08:12</t>
   </si>
   <si>
     <t>VAL-TC-247</t>
@@ -3244,7 +3244,7 @@
     <t>Validate ISO 8601 timestamp string format [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:48</t>
+    <t>2026-09-03 09:08:23</t>
   </si>
   <si>
     <t>VAL-TC-248</t>
@@ -3253,7 +3253,7 @@
     <t>Validate timezone string against IANA Time Zone Database [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:58</t>
+    <t>2026-09-03 09:08:33</t>
   </si>
   <si>
     <t>VAL-TC-249</t>
@@ -3262,7 +3262,7 @@
     <t>Reject invalid day of week index in availability (0-6 only) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:09</t>
+    <t>2026-09-03 09:08:44</t>
   </si>
   <si>
     <t>VAL-TC-250</t>
@@ -3271,7 +3271,7 @@
     <t>Validate weekly recurring availability start time is before end time [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:19</t>
+    <t>2026-09-03 09:08:54</t>
   </si>
   <si>
     <t>VAL-TC-251</t>
@@ -3280,7 +3280,7 @@
     <t>Validate SDP Offer session description schema structure [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:30</t>
+    <t>2026-09-03 09:09:05</t>
   </si>
   <si>
     <t>VAL-TC-252</t>
@@ -3289,7 +3289,7 @@
     <t>Validate SDP Answer session description schema structure [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:40</t>
+    <t>2026-09-03 09:09:15</t>
   </si>
   <si>
     <t>VAL-TC-253</t>
@@ -3298,7 +3298,7 @@
     <t>Validate ICE Candidate payload required keys (candidate, sdpMid, sdpMLineIndex) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:51</t>
+    <t>2026-09-03 09:09:26</t>
   </si>
   <si>
     <t>VAL-TC-254</t>
@@ -3307,7 +3307,7 @@
     <t>Reject malformed SDP string with corrupted headers [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:01</t>
+    <t>2026-09-03 09:09:36</t>
   </si>
   <si>
     <t>VAL-TC-255</t>
@@ -3316,7 +3316,7 @@
     <t>Validate WebRTC room ID format (alpha-numeric UUID string) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:12</t>
+    <t>2026-09-03 09:09:47</t>
   </si>
   <si>
     <t>VAL-TC-256</t>
@@ -3325,7 +3325,7 @@
     <t>Enforce maximum 2 participants in 1-on-1 swap room [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:22</t>
+    <t>2026-09-03 09:09:57</t>
   </si>
   <si>
     <t>VAL-TC-257</t>
@@ -3334,7 +3334,7 @@
     <t>Validate media stream tracks (audio/video) before attach [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:33</t>
+    <t>2026-09-03 09:10:08</t>
   </si>
   <si>
     <t>VAL-TC-258</t>
@@ -3343,7 +3343,7 @@
     <t>Validate screen share track kind equals "video" [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:43</t>
+    <t>2026-09-03 09:10:18</t>
   </si>
   <si>
     <t>VAL-TC-259</t>
@@ -3352,7 +3352,7 @@
     <t>Reject WebRTC signaling exchange when call session is closed [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:54</t>
+    <t>2026-09-03 09:10:29</t>
   </si>
   <si>
     <t>VAL-TC-260</t>
@@ -3361,7 +3361,7 @@
     <t>Validate signaling message timestamp within tolerance window (30s) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:04</t>
+    <t>2026-09-03 09:10:39</t>
   </si>
   <si>
     <t>VAL-TC-261</t>
@@ -3370,7 +3370,7 @@
     <t>Sanitize NoSQL injection operators ($gt, $ne, $where) in queries [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:15</t>
+    <t>2026-09-03 09:10:50</t>
   </si>
   <si>
     <t>VAL-TC-262</t>
@@ -3379,7 +3379,7 @@
     <t>Prevent SQL injection payload strings in text inputs [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:25</t>
+    <t>2026-09-03 09:11:00</t>
   </si>
   <si>
     <t>VAL-TC-263</t>
@@ -3388,7 +3388,7 @@
     <t>Prevent Javascript URI injection in href links [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:36</t>
+    <t>2026-09-03 09:11:11</t>
   </si>
   <si>
     <t>VAL-TC-264</t>
@@ -3397,7 +3397,7 @@
     <t>Validate data URLs format safety (image/png;base64 only) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:46</t>
+    <t>2026-09-03 09:11:21</t>
   </si>
   <si>
     <t>VAL-TC-265</t>
@@ -3406,7 +3406,7 @@
     <t>Prevent path traversal characters in file upload names (../..) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:57</t>
+    <t>2026-09-03 09:11:32</t>
   </si>
   <si>
     <t>VAL-TC-266</t>
@@ -3415,7 +3415,7 @@
     <t>Validate CORS origin header against allowed domain list [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:07</t>
+    <t>2026-09-03 09:11:42</t>
   </si>
   <si>
     <t>VAL-TC-267</t>
@@ -3424,7 +3424,7 @@
     <t>Prevent prototype pollution attacks on object merge [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:18</t>
+    <t>2026-09-03 09:11:53</t>
   </si>
   <si>
     <t>VAL-TC-268</t>
@@ -3433,7 +3433,7 @@
     <t>Validate JSON Web Token (JWT) signature algorithm (RS256/HS256) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:28</t>
+    <t>2026-09-03 09:12:03</t>
   </si>
   <si>
     <t>VAL-TC-269</t>
@@ -3442,7 +3442,7 @@
     <t>Prevent clickjacking with X-Frame-Options: SAMEORIGIN [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:39</t>
+    <t>2026-09-03 09:12:14</t>
   </si>
   <si>
     <t>VAL-TC-270</t>
@@ -3451,7 +3451,7 @@
     <t>Validate Content-Security-Policy (CSP) header directive compliance [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:49</t>
+    <t>2026-09-03 09:12:24</t>
   </si>
   <si>
     <t>VAL-TC-271</t>
@@ -3460,7 +3460,7 @@
     <t>Validate star rating integer value within range [1, 5] [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:00</t>
+    <t>2026-09-03 09:12:35</t>
   </si>
   <si>
     <t>VAL-TC-272</t>
@@ -3469,7 +3469,7 @@
     <t>Reject fractional star ratings not matching 0.5 step [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:10</t>
+    <t>2026-09-03 09:12:45</t>
   </si>
   <si>
     <t>VAL-TC-273</t>
@@ -3478,7 +3478,7 @@
     <t>Review comment minimum 10 characters requirement [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:21</t>
+    <t>2026-09-03 09:12:56</t>
   </si>
   <si>
     <t>VAL-TC-274</t>
@@ -3487,7 +3487,7 @@
     <t>Review comment maximum 1000 characters limit [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:31</t>
+    <t>2026-09-03 09:13:06</t>
   </si>
   <si>
     <t>VAL-TC-275</t>
@@ -3496,7 +3496,7 @@
     <t>Validate review tags array contains only approved endorsement tags [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:42</t>
+    <t>2026-09-03 09:13:17</t>
   </si>
   <si>
     <t>VAL-TC-276</t>
@@ -3505,7 +3505,7 @@
     <t>Prevent self-review submission (reviewer === reviewee) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:52</t>
+    <t>2026-09-03 09:13:27</t>
   </si>
   <si>
     <t>VAL-TC-277</t>
@@ -3514,7 +3514,7 @@
     <t>Validate review submission within 14 days of session completion [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:03</t>
+    <t>2026-09-03 09:13:38</t>
   </si>
   <si>
     <t>VAL-TC-278</t>
@@ -3523,7 +3523,7 @@
     <t>Sanitize review text against profanity filter dictionary [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:13</t>
+    <t>2026-09-03 09:13:48</t>
   </si>
   <si>
     <t>VAL-TC-279</t>
@@ -3532,7 +3532,7 @@
     <t>Validate review helpful vote payload structure [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:24</t>
+    <t>2026-09-03 09:13:59</t>
   </si>
   <si>
     <t>VAL-TC-280</t>
@@ -3541,7 +3541,7 @@
     <t>Prevent user from voting on their own review [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:34</t>
+    <t>2026-09-03 09:14:09</t>
   </si>
   <si>
     <t>VAL-TC-281</t>
@@ -3550,7 +3550,7 @@
     <t>User Document schema requires uid, email, createdAt, displayName [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:45</t>
+    <t>2026-09-03 09:14:20</t>
   </si>
   <si>
     <t>VAL-TC-282</t>
@@ -3559,7 +3559,7 @@
     <t>Swap Request doc requires fromUser, toUser, status, offeredSkill [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:55</t>
+    <t>2026-09-03 09:14:30</t>
   </si>
   <si>
     <t>VAL-TC-283</t>
@@ -3568,7 +3568,7 @@
     <t>Session Booking doc requires participants, startTime, endTime, status [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:06</t>
+    <t>2026-09-03 09:14:41</t>
   </si>
   <si>
     <t>VAL-TC-284</t>
@@ -3577,7 +3577,7 @@
     <t>Message doc requires senderId, text, createdAt, conversationId [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:16</t>
+    <t>2026-09-03 09:14:51</t>
   </si>
   <si>
     <t>VAL-TC-285</t>
@@ -3586,7 +3586,7 @@
     <t>Review doc requires authorId, targetUserId, rating, comment, createdAt [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:27</t>
+    <t>2026-09-03 09:15:02</t>
   </si>
   <si>
     <t>VAL-TC-286</t>
@@ -3595,7 +3595,7 @@
     <t>Notification doc requires userId, type, title, read, timestamp [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:37</t>
+    <t>2026-09-03 09:15:12</t>
   </si>
   <si>
     <t>VAL-TC-287</t>
@@ -3604,7 +3604,7 @@
     <t>Ensure createdAt timestamp is a valid Firestore Timestamp or Date [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:48</t>
+    <t>2026-09-03 09:15:23</t>
   </si>
   <si>
     <t>VAL-TC-288</t>
@@ -3613,7 +3613,7 @@
     <t>Enforce status field enum values in Swap Request ["pending", "accepted", "declined", "cancelled"] [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:58</t>
+    <t>2026-09-03 09:15:33</t>
   </si>
   <si>
     <t>VAL-TC-289</t>
@@ -3622,7 +3622,7 @@
     <t>Enforce status field enum values in Session ["scheduled", "in_progress", "completed", "cancelled"] [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:09</t>
+    <t>2026-09-03 09:15:44</t>
   </si>
   <si>
     <t>VAL-TC-290</t>
@@ -3631,7 +3631,7 @@
     <t>Ensure user credit balance is non-negative integer [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:19</t>
+    <t>2026-09-03 09:15:54</t>
   </si>
   <si>
     <t>VAL-TC-291</t>
@@ -3640,7 +3640,7 @@
     <t>Handle null user profile in component without throwing Uncaught TypeError [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:30</t>
+    <t>2026-09-03 09:16:05</t>
   </si>
   <si>
     <t>VAL-TC-292</t>
@@ -3649,7 +3649,7 @@
     <t>Handle empty array for skills list without breaking .map() [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:40</t>
+    <t>2026-09-03 09:16:15</t>
   </si>
   <si>
     <t>VAL-TC-293</t>
@@ -3658,7 +3658,7 @@
     <t>Handle undefined avatar photoURL by rendering initials fallback [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:51</t>
+    <t>2026-09-03 09:16:26</t>
   </si>
   <si>
     <t>VAL-TC-294</t>
@@ -3667,7 +3667,7 @@
     <t>Handle extremely long single-word string in message (word-break test) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:01</t>
+    <t>2026-09-03 09:16:36</t>
   </si>
   <si>
     <t>VAL-TC-295</t>
@@ -3676,7 +3676,7 @@
     <t>Handle unicode emojis and multi-byte characters in all text inputs (🚀🔥🎉) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:12</t>
+    <t>2026-09-03 09:16:47</t>
   </si>
   <si>
     <t>VAL-TC-296</t>
@@ -3685,7 +3685,7 @@
     <t>Handle right-to-left (RTL) text strings (Arabic, Hebrew) gracefully [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:22</t>
+    <t>2026-09-03 09:16:57</t>
   </si>
   <si>
     <t>VAL-TC-297</t>
@@ -3694,7 +3694,7 @@
     <t>Handle leap year date calculations (e.g. Feb 29 2028) in calendar [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:33</t>
+    <t>2026-09-03 09:17:08</t>
   </si>
   <si>
     <t>VAL-TC-298</t>
@@ -3703,7 +3703,7 @@
     <t>Handle daylight saving time (DST) transition offsets in scheduling [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:43</t>
+    <t>2026-09-03 09:17:18</t>
   </si>
   <si>
     <t>VAL-TC-299</t>
@@ -3712,7 +3712,7 @@
     <t>Handle floating point precision rounding in swap hours (0.1 + 0.2) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:54</t>
+    <t>2026-09-03 09:17:29</t>
   </si>
   <si>
     <t>VAL-TC-300</t>
@@ -3721,7 +3721,7 @@
     <t>Handle rapid consecutive button clicks (double click prevention) [Security &amp; Injection Sanitizer Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:10:04</t>
+    <t>2026-09-03 09:17:39</t>
   </si>
 </sst>
 </file>
@@ -4263,7 +4263,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4304,7 +4304,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -4345,7 +4345,7 @@
         <v>36</v>
       </c>
       <c r="J4" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>22</v>
@@ -4386,7 +4386,7 @@
         <v>42</v>
       </c>
       <c r="J5" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>22</v>
@@ -4427,7 +4427,7 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -4468,7 +4468,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>22</v>
@@ -4509,7 +4509,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -4550,7 +4550,7 @@
         <v>67</v>
       </c>
       <c r="J9" s="5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -4591,7 +4591,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -4632,7 +4632,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="5">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -4673,7 +4673,7 @@
         <v>87</v>
       </c>
       <c r="J12" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -4714,7 +4714,7 @@
         <v>93</v>
       </c>
       <c r="J13" s="5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -4837,7 +4837,7 @@
         <v>111</v>
       </c>
       <c r="J16" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -4878,7 +4878,7 @@
         <v>117</v>
       </c>
       <c r="J17" s="5">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -4919,7 +4919,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>22</v>
@@ -4960,7 +4960,7 @@
         <v>129</v>
       </c>
       <c r="J19" s="5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -5001,7 +5001,7 @@
         <v>135</v>
       </c>
       <c r="J20" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5042,7 +5042,7 @@
         <v>141</v>
       </c>
       <c r="J21" s="5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5083,7 +5083,7 @@
         <v>149</v>
       </c>
       <c r="J22" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -5124,7 +5124,7 @@
         <v>155</v>
       </c>
       <c r="J23" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>22</v>
@@ -5165,7 +5165,7 @@
         <v>161</v>
       </c>
       <c r="J24" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -5206,7 +5206,7 @@
         <v>167</v>
       </c>
       <c r="J25" s="5">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -5247,7 +5247,7 @@
         <v>173</v>
       </c>
       <c r="J26" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -5288,7 +5288,7 @@
         <v>179</v>
       </c>
       <c r="J27" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -5329,7 +5329,7 @@
         <v>185</v>
       </c>
       <c r="J28" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -5370,7 +5370,7 @@
         <v>191</v>
       </c>
       <c r="J29" s="5">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -5411,7 +5411,7 @@
         <v>197</v>
       </c>
       <c r="J30" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -5452,7 +5452,7 @@
         <v>203</v>
       </c>
       <c r="J31" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -5493,7 +5493,7 @@
         <v>211</v>
       </c>
       <c r="J32" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -5534,7 +5534,7 @@
         <v>217</v>
       </c>
       <c r="J33" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -5575,7 +5575,7 @@
         <v>223</v>
       </c>
       <c r="J34" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -5616,7 +5616,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -5657,7 +5657,7 @@
         <v>235</v>
       </c>
       <c r="J36" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -5698,7 +5698,7 @@
         <v>241</v>
       </c>
       <c r="J37" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>22</v>
@@ -5739,7 +5739,7 @@
         <v>247</v>
       </c>
       <c r="J38" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>22</v>
@@ -5780,7 +5780,7 @@
         <v>253</v>
       </c>
       <c r="J39" s="5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -5821,7 +5821,7 @@
         <v>259</v>
       </c>
       <c r="J40" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -5862,7 +5862,7 @@
         <v>265</v>
       </c>
       <c r="J41" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -5903,7 +5903,7 @@
         <v>273</v>
       </c>
       <c r="J42" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>22</v>
@@ -5944,7 +5944,7 @@
         <v>279</v>
       </c>
       <c r="J43" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -5985,7 +5985,7 @@
         <v>285</v>
       </c>
       <c r="J44" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>22</v>
@@ -6026,7 +6026,7 @@
         <v>291</v>
       </c>
       <c r="J45" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6067,7 +6067,7 @@
         <v>297</v>
       </c>
       <c r="J46" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -6108,7 +6108,7 @@
         <v>303</v>
       </c>
       <c r="J47" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -6149,7 +6149,7 @@
         <v>309</v>
       </c>
       <c r="J48" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -6190,7 +6190,7 @@
         <v>315</v>
       </c>
       <c r="J49" s="5">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -6231,7 +6231,7 @@
         <v>321</v>
       </c>
       <c r="J50" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -6313,7 +6313,7 @@
         <v>335</v>
       </c>
       <c r="J52" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>22</v>
@@ -6354,7 +6354,7 @@
         <v>335</v>
       </c>
       <c r="J53" s="5">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -6395,7 +6395,7 @@
         <v>345</v>
       </c>
       <c r="J54" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -6436,7 +6436,7 @@
         <v>351</v>
       </c>
       <c r="J55" s="5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>22</v>
@@ -6477,7 +6477,7 @@
         <v>357</v>
       </c>
       <c r="J56" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -6518,7 +6518,7 @@
         <v>363</v>
       </c>
       <c r="J57" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -6559,7 +6559,7 @@
         <v>369</v>
       </c>
       <c r="J58" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -6600,7 +6600,7 @@
         <v>375</v>
       </c>
       <c r="J59" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -6641,7 +6641,7 @@
         <v>381</v>
       </c>
       <c r="J60" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -6682,7 +6682,7 @@
         <v>387</v>
       </c>
       <c r="J61" s="5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -6723,7 +6723,7 @@
         <v>395</v>
       </c>
       <c r="J62" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -6764,7 +6764,7 @@
         <v>401</v>
       </c>
       <c r="J63" s="5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -6805,7 +6805,7 @@
         <v>407</v>
       </c>
       <c r="J64" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>22</v>
@@ -6846,7 +6846,7 @@
         <v>413</v>
       </c>
       <c r="J65" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -6887,7 +6887,7 @@
         <v>419</v>
       </c>
       <c r="J66" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -6928,7 +6928,7 @@
         <v>425</v>
       </c>
       <c r="J67" s="5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -6969,7 +6969,7 @@
         <v>431</v>
       </c>
       <c r="J68" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7010,7 +7010,7 @@
         <v>437</v>
       </c>
       <c r="J69" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7051,7 +7051,7 @@
         <v>443</v>
       </c>
       <c r="J70" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7092,7 +7092,7 @@
         <v>449</v>
       </c>
       <c r="J71" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>22</v>
@@ -7133,7 +7133,7 @@
         <v>457</v>
       </c>
       <c r="J72" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>22</v>
@@ -7174,7 +7174,7 @@
         <v>463</v>
       </c>
       <c r="J73" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -7215,7 +7215,7 @@
         <v>469</v>
       </c>
       <c r="J74" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -7256,7 +7256,7 @@
         <v>475</v>
       </c>
       <c r="J75" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -7297,7 +7297,7 @@
         <v>481</v>
       </c>
       <c r="J76" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -7338,7 +7338,7 @@
         <v>487</v>
       </c>
       <c r="J77" s="5">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -7379,7 +7379,7 @@
         <v>493</v>
       </c>
       <c r="J78" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -7420,7 +7420,7 @@
         <v>499</v>
       </c>
       <c r="J79" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -7461,7 +7461,7 @@
         <v>505</v>
       </c>
       <c r="J80" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -7502,7 +7502,7 @@
         <v>511</v>
       </c>
       <c r="J81" s="5">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -7543,7 +7543,7 @@
         <v>519</v>
       </c>
       <c r="J82" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -7584,7 +7584,7 @@
         <v>525</v>
       </c>
       <c r="J83" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -7625,7 +7625,7 @@
         <v>531</v>
       </c>
       <c r="J84" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -7666,7 +7666,7 @@
         <v>537</v>
       </c>
       <c r="J85" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>22</v>
@@ -7707,7 +7707,7 @@
         <v>543</v>
       </c>
       <c r="J86" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>22</v>
@@ -7748,7 +7748,7 @@
         <v>549</v>
       </c>
       <c r="J87" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -7789,7 +7789,7 @@
         <v>555</v>
       </c>
       <c r="J88" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -7830,7 +7830,7 @@
         <v>561</v>
       </c>
       <c r="J89" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -7871,7 +7871,7 @@
         <v>567</v>
       </c>
       <c r="J90" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>22</v>
@@ -7912,7 +7912,7 @@
         <v>573</v>
       </c>
       <c r="J91" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -7953,7 +7953,7 @@
         <v>581</v>
       </c>
       <c r="J92" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -7994,7 +7994,7 @@
         <v>587</v>
       </c>
       <c r="J93" s="5">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8035,7 +8035,7 @@
         <v>593</v>
       </c>
       <c r="J94" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8076,7 +8076,7 @@
         <v>599</v>
       </c>
       <c r="J95" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -8117,7 +8117,7 @@
         <v>605</v>
       </c>
       <c r="J96" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -8158,7 +8158,7 @@
         <v>611</v>
       </c>
       <c r="J97" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>22</v>
@@ -8199,7 +8199,7 @@
         <v>617</v>
       </c>
       <c r="J98" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -8240,7 +8240,7 @@
         <v>623</v>
       </c>
       <c r="J99" s="5">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -8281,7 +8281,7 @@
         <v>629</v>
       </c>
       <c r="J100" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -8322,7 +8322,7 @@
         <v>635</v>
       </c>
       <c r="J101" s="5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -8363,7 +8363,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -8404,7 +8404,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="5">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -8486,7 +8486,7 @@
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -8527,7 +8527,7 @@
         <v>49</v>
       </c>
       <c r="J106" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -8568,7 +8568,7 @@
         <v>55</v>
       </c>
       <c r="J107" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -8650,7 +8650,7 @@
         <v>67</v>
       </c>
       <c r="J109" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -8691,7 +8691,7 @@
         <v>73</v>
       </c>
       <c r="J110" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -8732,7 +8732,7 @@
         <v>79</v>
       </c>
       <c r="J111" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -8773,7 +8773,7 @@
         <v>87</v>
       </c>
       <c r="J112" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -8814,7 +8814,7 @@
         <v>93</v>
       </c>
       <c r="J113" s="5">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>22</v>
@@ -8855,7 +8855,7 @@
         <v>99</v>
       </c>
       <c r="J114" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -8896,7 +8896,7 @@
         <v>105</v>
       </c>
       <c r="J115" s="5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -8937,7 +8937,7 @@
         <v>111</v>
       </c>
       <c r="J116" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -8978,7 +8978,7 @@
         <v>117</v>
       </c>
       <c r="J117" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9019,7 +9019,7 @@
         <v>123</v>
       </c>
       <c r="J118" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9060,7 +9060,7 @@
         <v>129</v>
       </c>
       <c r="J119" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -9101,7 +9101,7 @@
         <v>135</v>
       </c>
       <c r="J120" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -9142,7 +9142,7 @@
         <v>141</v>
       </c>
       <c r="J121" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -9183,7 +9183,7 @@
         <v>149</v>
       </c>
       <c r="J122" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>22</v>
@@ -9224,7 +9224,7 @@
         <v>155</v>
       </c>
       <c r="J123" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K123" s="4" t="s">
         <v>22</v>
@@ -9265,7 +9265,7 @@
         <v>161</v>
       </c>
       <c r="J124" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -9306,7 +9306,7 @@
         <v>167</v>
       </c>
       <c r="J125" s="5">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -9347,7 +9347,7 @@
         <v>173</v>
       </c>
       <c r="J126" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -9388,7 +9388,7 @@
         <v>179</v>
       </c>
       <c r="J127" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -9429,7 +9429,7 @@
         <v>185</v>
       </c>
       <c r="J128" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -9470,7 +9470,7 @@
         <v>191</v>
       </c>
       <c r="J129" s="5">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -9511,7 +9511,7 @@
         <v>197</v>
       </c>
       <c r="J130" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -9552,7 +9552,7 @@
         <v>203</v>
       </c>
       <c r="J131" s="5">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -9593,7 +9593,7 @@
         <v>211</v>
       </c>
       <c r="J132" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -9634,7 +9634,7 @@
         <v>217</v>
       </c>
       <c r="J133" s="5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -9675,7 +9675,7 @@
         <v>223</v>
       </c>
       <c r="J134" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -9716,7 +9716,7 @@
         <v>229</v>
       </c>
       <c r="J135" s="5">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>22</v>
@@ -9757,7 +9757,7 @@
         <v>235</v>
       </c>
       <c r="J136" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -9798,7 +9798,7 @@
         <v>241</v>
       </c>
       <c r="J137" s="5">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -9839,7 +9839,7 @@
         <v>247</v>
       </c>
       <c r="J138" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -9880,7 +9880,7 @@
         <v>253</v>
       </c>
       <c r="J139" s="5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -9921,7 +9921,7 @@
         <v>259</v>
       </c>
       <c r="J140" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -9962,7 +9962,7 @@
         <v>265</v>
       </c>
       <c r="J141" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10003,7 +10003,7 @@
         <v>273</v>
       </c>
       <c r="J142" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>22</v>
@@ -10044,7 +10044,7 @@
         <v>279</v>
       </c>
       <c r="J143" s="5">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10126,7 +10126,7 @@
         <v>291</v>
       </c>
       <c r="J145" s="5">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -10167,7 +10167,7 @@
         <v>297</v>
       </c>
       <c r="J146" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>22</v>
@@ -10208,7 +10208,7 @@
         <v>303</v>
       </c>
       <c r="J147" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -10249,7 +10249,7 @@
         <v>309</v>
       </c>
       <c r="J148" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -10290,7 +10290,7 @@
         <v>315</v>
       </c>
       <c r="J149" s="5">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -10372,7 +10372,7 @@
         <v>327</v>
       </c>
       <c r="J151" s="5">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -10413,7 +10413,7 @@
         <v>335</v>
       </c>
       <c r="J152" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -10454,7 +10454,7 @@
         <v>335</v>
       </c>
       <c r="J153" s="5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -10495,7 +10495,7 @@
         <v>345</v>
       </c>
       <c r="J154" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -10536,7 +10536,7 @@
         <v>351</v>
       </c>
       <c r="J155" s="5">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -10577,7 +10577,7 @@
         <v>357</v>
       </c>
       <c r="J156" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -10618,7 +10618,7 @@
         <v>363</v>
       </c>
       <c r="J157" s="5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>22</v>
@@ -10659,7 +10659,7 @@
         <v>369</v>
       </c>
       <c r="J158" s="2">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -10700,7 +10700,7 @@
         <v>375</v>
       </c>
       <c r="J159" s="5">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -10741,7 +10741,7 @@
         <v>381</v>
       </c>
       <c r="J160" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -10782,7 +10782,7 @@
         <v>387</v>
       </c>
       <c r="J161" s="5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -10823,7 +10823,7 @@
         <v>395</v>
       </c>
       <c r="J162" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -10864,7 +10864,7 @@
         <v>401</v>
       </c>
       <c r="J163" s="5">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -10905,7 +10905,7 @@
         <v>407</v>
       </c>
       <c r="J164" s="2">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -10946,7 +10946,7 @@
         <v>413</v>
       </c>
       <c r="J165" s="5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>22</v>
@@ -10987,7 +10987,7 @@
         <v>419</v>
       </c>
       <c r="J166" s="2">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11028,7 +11028,7 @@
         <v>425</v>
       </c>
       <c r="J167" s="5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11069,7 +11069,7 @@
         <v>431</v>
       </c>
       <c r="J168" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -11110,7 +11110,7 @@
         <v>437</v>
       </c>
       <c r="J169" s="5">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -11151,7 +11151,7 @@
         <v>443</v>
       </c>
       <c r="J170" s="2">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -11192,7 +11192,7 @@
         <v>449</v>
       </c>
       <c r="J171" s="5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -11233,7 +11233,7 @@
         <v>457</v>
       </c>
       <c r="J172" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -11315,7 +11315,7 @@
         <v>469</v>
       </c>
       <c r="J174" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -11356,7 +11356,7 @@
         <v>475</v>
       </c>
       <c r="J175" s="5">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -11397,7 +11397,7 @@
         <v>481</v>
       </c>
       <c r="J176" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -11438,7 +11438,7 @@
         <v>487</v>
       </c>
       <c r="J177" s="5">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -11479,7 +11479,7 @@
         <v>493</v>
       </c>
       <c r="J178" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -11520,7 +11520,7 @@
         <v>499</v>
       </c>
       <c r="J179" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -11561,7 +11561,7 @@
         <v>505</v>
       </c>
       <c r="J180" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -11602,7 +11602,7 @@
         <v>511</v>
       </c>
       <c r="J181" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -11643,7 +11643,7 @@
         <v>519</v>
       </c>
       <c r="J182" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>22</v>
@@ -11684,7 +11684,7 @@
         <v>525</v>
       </c>
       <c r="J183" s="5">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -11725,7 +11725,7 @@
         <v>531</v>
       </c>
       <c r="J184" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -11766,7 +11766,7 @@
         <v>537</v>
       </c>
       <c r="J185" s="5">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -11807,7 +11807,7 @@
         <v>543</v>
       </c>
       <c r="J186" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>22</v>
@@ -11848,7 +11848,7 @@
         <v>549</v>
       </c>
       <c r="J187" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>22</v>
@@ -11889,7 +11889,7 @@
         <v>555</v>
       </c>
       <c r="J188" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -11930,7 +11930,7 @@
         <v>561</v>
       </c>
       <c r="J189" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -11971,7 +11971,7 @@
         <v>567</v>
       </c>
       <c r="J190" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12012,7 +12012,7 @@
         <v>573</v>
       </c>
       <c r="J191" s="5">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12053,7 +12053,7 @@
         <v>581</v>
       </c>
       <c r="J192" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12094,7 +12094,7 @@
         <v>587</v>
       </c>
       <c r="J193" s="5">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -12135,7 +12135,7 @@
         <v>593</v>
       </c>
       <c r="J194" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -12176,7 +12176,7 @@
         <v>599</v>
       </c>
       <c r="J195" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>22</v>
@@ -12217,7 +12217,7 @@
         <v>605</v>
       </c>
       <c r="J196" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -12258,7 +12258,7 @@
         <v>611</v>
       </c>
       <c r="J197" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>22</v>
@@ -12299,7 +12299,7 @@
         <v>617</v>
       </c>
       <c r="J198" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -12340,7 +12340,7 @@
         <v>623</v>
       </c>
       <c r="J199" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -12381,7 +12381,7 @@
         <v>629</v>
       </c>
       <c r="J200" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -12422,7 +12422,7 @@
         <v>635</v>
       </c>
       <c r="J201" s="5">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -12463,7 +12463,7 @@
         <v>21</v>
       </c>
       <c r="J202" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -12504,7 +12504,7 @@
         <v>29</v>
       </c>
       <c r="J203" s="5">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -12545,7 +12545,7 @@
         <v>36</v>
       </c>
       <c r="J204" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>22</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="J206" s="2">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -12668,7 +12668,7 @@
         <v>55</v>
       </c>
       <c r="J207" s="5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -12709,7 +12709,7 @@
         <v>61</v>
       </c>
       <c r="J208" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -12750,7 +12750,7 @@
         <v>67</v>
       </c>
       <c r="J209" s="5">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -12791,7 +12791,7 @@
         <v>73</v>
       </c>
       <c r="J210" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -12832,7 +12832,7 @@
         <v>79</v>
       </c>
       <c r="J211" s="5">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -12873,7 +12873,7 @@
         <v>87</v>
       </c>
       <c r="J212" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -12914,7 +12914,7 @@
         <v>93</v>
       </c>
       <c r="J213" s="5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>22</v>
@@ -12955,7 +12955,7 @@
         <v>99</v>
       </c>
       <c r="J214" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>22</v>
@@ -12996,7 +12996,7 @@
         <v>105</v>
       </c>
       <c r="J215" s="5">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>22</v>
@@ -13037,7 +13037,7 @@
         <v>111</v>
       </c>
       <c r="J216" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13078,7 +13078,7 @@
         <v>117</v>
       </c>
       <c r="J217" s="5">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -13119,7 +13119,7 @@
         <v>123</v>
       </c>
       <c r="J218" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -13160,7 +13160,7 @@
         <v>129</v>
       </c>
       <c r="J219" s="5">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -13201,7 +13201,7 @@
         <v>135</v>
       </c>
       <c r="J220" s="2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -13283,7 +13283,7 @@
         <v>149</v>
       </c>
       <c r="J222" s="2">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>22</v>
@@ -13365,7 +13365,7 @@
         <v>161</v>
       </c>
       <c r="J224" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -13406,7 +13406,7 @@
         <v>167</v>
       </c>
       <c r="J225" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -13447,7 +13447,7 @@
         <v>173</v>
       </c>
       <c r="J226" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -13488,7 +13488,7 @@
         <v>179</v>
       </c>
       <c r="J227" s="5">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -13529,7 +13529,7 @@
         <v>185</v>
       </c>
       <c r="J228" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -13570,7 +13570,7 @@
         <v>191</v>
       </c>
       <c r="J229" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>22</v>
@@ -13611,7 +13611,7 @@
         <v>197</v>
       </c>
       <c r="J230" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -13652,7 +13652,7 @@
         <v>203</v>
       </c>
       <c r="J231" s="5">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -13693,7 +13693,7 @@
         <v>211</v>
       </c>
       <c r="J232" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -13734,7 +13734,7 @@
         <v>217</v>
       </c>
       <c r="J233" s="5">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -13775,7 +13775,7 @@
         <v>223</v>
       </c>
       <c r="J234" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -13816,7 +13816,7 @@
         <v>229</v>
       </c>
       <c r="J235" s="5">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -13939,7 +13939,7 @@
         <v>247</v>
       </c>
       <c r="J238" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -13980,7 +13980,7 @@
         <v>253</v>
       </c>
       <c r="J239" s="5">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14021,7 +14021,7 @@
         <v>259</v>
       </c>
       <c r="J240" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14062,7 +14062,7 @@
         <v>265</v>
       </c>
       <c r="J241" s="5">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>22</v>
@@ -14103,7 +14103,7 @@
         <v>273</v>
       </c>
       <c r="J242" s="2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -14144,7 +14144,7 @@
         <v>279</v>
       </c>
       <c r="J243" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -14185,7 +14185,7 @@
         <v>285</v>
       </c>
       <c r="J244" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -14226,7 +14226,7 @@
         <v>291</v>
       </c>
       <c r="J245" s="5">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -14267,7 +14267,7 @@
         <v>297</v>
       </c>
       <c r="J246" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -14308,7 +14308,7 @@
         <v>303</v>
       </c>
       <c r="J247" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -14349,7 +14349,7 @@
         <v>309</v>
       </c>
       <c r="J248" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -14390,7 +14390,7 @@
         <v>315</v>
       </c>
       <c r="J249" s="5">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -14431,7 +14431,7 @@
         <v>321</v>
       </c>
       <c r="J250" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -14472,7 +14472,7 @@
         <v>327</v>
       </c>
       <c r="J251" s="5">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -14513,7 +14513,7 @@
         <v>335</v>
       </c>
       <c r="J252" s="2">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -14554,7 +14554,7 @@
         <v>335</v>
       </c>
       <c r="J253" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -14595,7 +14595,7 @@
         <v>345</v>
       </c>
       <c r="J254" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -14636,7 +14636,7 @@
         <v>351</v>
       </c>
       <c r="J255" s="5">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -14677,7 +14677,7 @@
         <v>357</v>
       </c>
       <c r="J256" s="2">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -14718,7 +14718,7 @@
         <v>363</v>
       </c>
       <c r="J257" s="5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>22</v>
@@ -14759,7 +14759,7 @@
         <v>369</v>
       </c>
       <c r="J258" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -14800,7 +14800,7 @@
         <v>375</v>
       </c>
       <c r="J259" s="5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -14841,7 +14841,7 @@
         <v>381</v>
       </c>
       <c r="J260" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -14882,7 +14882,7 @@
         <v>387</v>
       </c>
       <c r="J261" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -14923,7 +14923,7 @@
         <v>395</v>
       </c>
       <c r="J262" s="2">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -14964,7 +14964,7 @@
         <v>401</v>
       </c>
       <c r="J263" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15005,7 +15005,7 @@
         <v>407</v>
       </c>
       <c r="J264" s="2">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15046,7 +15046,7 @@
         <v>413</v>
       </c>
       <c r="J265" s="5">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>22</v>
@@ -15087,7 +15087,7 @@
         <v>419</v>
       </c>
       <c r="J266" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -15128,7 +15128,7 @@
         <v>425</v>
       </c>
       <c r="J267" s="5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -15169,7 +15169,7 @@
         <v>431</v>
       </c>
       <c r="J268" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -15210,7 +15210,7 @@
         <v>437</v>
       </c>
       <c r="J269" s="5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -15251,7 +15251,7 @@
         <v>443</v>
       </c>
       <c r="J270" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -15292,7 +15292,7 @@
         <v>449</v>
       </c>
       <c r="J271" s="5">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -15333,7 +15333,7 @@
         <v>457</v>
       </c>
       <c r="J272" s="2">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -15374,7 +15374,7 @@
         <v>463</v>
       </c>
       <c r="J273" s="5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -15415,7 +15415,7 @@
         <v>469</v>
       </c>
       <c r="J274" s="2">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>22</v>
@@ -15456,7 +15456,7 @@
         <v>475</v>
       </c>
       <c r="J275" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -15497,7 +15497,7 @@
         <v>481</v>
       </c>
       <c r="J276" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -15538,7 +15538,7 @@
         <v>487</v>
       </c>
       <c r="J277" s="5">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -15579,7 +15579,7 @@
         <v>493</v>
       </c>
       <c r="J278" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -15620,7 +15620,7 @@
         <v>499</v>
       </c>
       <c r="J279" s="5">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -15661,7 +15661,7 @@
         <v>505</v>
       </c>
       <c r="J280" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -15702,7 +15702,7 @@
         <v>511</v>
       </c>
       <c r="J281" s="5">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -15743,7 +15743,7 @@
         <v>519</v>
       </c>
       <c r="J282" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -15784,7 +15784,7 @@
         <v>525</v>
       </c>
       <c r="J283" s="5">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -15825,7 +15825,7 @@
         <v>531</v>
       </c>
       <c r="J284" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -15866,7 +15866,7 @@
         <v>537</v>
       </c>
       <c r="J285" s="5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -15907,7 +15907,7 @@
         <v>543</v>
       </c>
       <c r="J286" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -15948,7 +15948,7 @@
         <v>549</v>
       </c>
       <c r="J287" s="5">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -15989,7 +15989,7 @@
         <v>555</v>
       </c>
       <c r="J288" s="2">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16030,7 +16030,7 @@
         <v>561</v>
       </c>
       <c r="J289" s="5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16071,7 +16071,7 @@
         <v>567</v>
       </c>
       <c r="J290" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -16112,7 +16112,7 @@
         <v>573</v>
       </c>
       <c r="J291" s="5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -16153,7 +16153,7 @@
         <v>581</v>
       </c>
       <c r="J292" s="2">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -16194,7 +16194,7 @@
         <v>587</v>
       </c>
       <c r="J293" s="5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -16235,7 +16235,7 @@
         <v>593</v>
       </c>
       <c r="J294" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -16276,7 +16276,7 @@
         <v>599</v>
       </c>
       <c r="J295" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>22</v>
@@ -16317,7 +16317,7 @@
         <v>605</v>
       </c>
       <c r="J296" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -16358,7 +16358,7 @@
         <v>611</v>
       </c>
       <c r="J297" s="5">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>22</v>
@@ -16399,7 +16399,7 @@
         <v>617</v>
       </c>
       <c r="J298" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -16440,7 +16440,7 @@
         <v>623</v>
       </c>
       <c r="J299" s="5">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -16522,7 +16522,7 @@
         <v>635</v>
       </c>
       <c r="J301" s="5">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
